--- a/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="230">
   <si>
     <t>Property</t>
   </si>
@@ -538,6 +538,22 @@
   </si>
   <si>
     <t>Condition.bodySite</t>
+  </si>
+  <si>
+    <t>Diagnose.DetaillierteAnatomischeStruktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(BodyStructure)
+</t>
+  </si>
+  <si>
+    <t>Detaillierte anatomische Struktur</t>
+  </si>
+  <si>
+    <t>Detaillierte Angaben zu der patientenbezogenen anatomischen Struktur oder Lokalisation, auf die sich die Diagnose bezieht. Das Element kann verwendet werden, wenn die kodierte Angabe der Körperstelle allein nicht die für den Anwendungsfall erforderliche Genauigkeit bietet.</t>
+  </si>
+  <si>
+    <t>Condition.bodySite.extension('http://hl7.org/fhir/StructureDefinition/bodySite').valueReference</t>
   </si>
   <si>
     <t>Diagnose.Freitextbeschreibung</t>
@@ -1007,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.1875" customWidth="true" bestFit="true"/>
@@ -1020,7 +1036,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="21.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4505,7 +4521,7 @@
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
@@ -4517,13 +4533,13 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4580,7 +4596,7 @@
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -4589,15 +4605,15 @@
         <v>75</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4608,7 +4624,7 @@
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>75</v>
@@ -4623,10 +4639,10 @@
         <v>85</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4677,13 +4693,13 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>75</v>
@@ -4692,15 +4708,15 @@
         <v>75</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4711,7 +4727,7 @@
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -4723,13 +4739,13 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4780,13 +4796,13 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>75</v>
@@ -4795,15 +4811,15 @@
         <v>75</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4826,13 +4842,13 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4883,7 +4899,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -4895,18 +4911,18 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4929,13 +4945,13 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4986,7 +5002,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -4998,29 +5014,29 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
@@ -5032,17 +5048,15 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5079,31 +5093,31 @@
         <v>75</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5111,14 +5125,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5131,26 +5145,24 @@
         <v>75</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -5186,19 +5198,19 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5218,42 +5230,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -5301,30 +5317,30 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>193</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5347,13 +5363,13 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>86</v>
+        <v>196</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>87</v>
+        <v>197</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5404,7 +5420,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5416,29 +5432,29 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -5450,17 +5466,15 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5497,31 +5511,31 @@
         <v>75</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
@@ -5529,14 +5543,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -5549,26 +5563,24 @@
         <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="O44" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
@@ -5604,19 +5616,19 @@
         <v>75</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5636,42 +5648,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -5719,30 +5735,30 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>200</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5765,13 +5781,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5822,7 +5838,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -5837,15 +5853,15 @@
         <v>75</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5856,7 +5872,7 @@
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>75</v>
@@ -5868,13 +5884,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5925,30 +5941,30 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>75</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5959,7 +5975,7 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
@@ -5971,13 +5987,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6028,19 +6044,19 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
@@ -6048,21 +6064,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -6074,17 +6090,15 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6121,31 +6135,31 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6153,14 +6167,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6173,26 +6187,24 @@
         <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="O50" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
@@ -6228,19 +6240,19 @@
         <v>75</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6260,42 +6272,46 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
       </c>
@@ -6343,30 +6359,30 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>212</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6392,10 +6408,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6446,7 +6462,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6461,15 +6477,15 @@
         <v>75</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6492,10 +6508,10 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>219</v>
@@ -6549,7 +6565,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6580,7 +6596,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>84</v>
@@ -6595,13 +6611,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6655,7 +6671,7 @@
         <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>84</v>
@@ -6667,7 +6683,110 @@
         <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-dev</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="228">
   <si>
     <t>Property</t>
   </si>
@@ -601,9 +601,6 @@
     <t>Hier kann der Klinisch Relevante Zeitraum beziehungsweise die Lebensphase einer Erkrankung angegeben werden. Datumsangaben zu Diagnosen können in unterschiedlicher Präzision vorhanden sein.</t>
   </si>
   <si>
-    <t>Condition.onset[x]</t>
-  </si>
-  <si>
     <t>Diagnose.KlinischRelevanterZeitraum.id</t>
   </si>
   <si>
@@ -620,9 +617,6 @@
   </si>
   <si>
     <t>Der Zeitraum wird durch zwei Datumsangaben beschrieben, das heißt, von wann bis wann ein Patient an der diagnostizierten Krankheit litt. Über den Zeitraum kann auch ausgedrückt werden, seit wann ein Patient an einer Krankheit leidet, indem nur das Startdatum des Zeitraums angegeben wird. Das Startdatum des Zeitraums kann abweichen von dem Diagnosedatum. Datumsangaben zu Diagnosen können in unterschiedlicher Präzision vorhanden sein.</t>
-  </si>
-  <si>
-    <t>Condition.onsetPeriod</t>
   </si>
   <si>
     <t>Diagnose.KlinischRelevanterZeitraum.Zeitraum.id</t>
@@ -644,7 +638,7 @@
     <t>Startdatum</t>
   </si>
   <si>
-    <t>Condition.onsetPeriod.start</t>
+    <t>Condition.onsetDateTime</t>
   </si>
   <si>
     <t>Diagnose.KlinischRelevanterZeitraum.Zeitraum.bis</t>
@@ -653,7 +647,7 @@
     <t>Enddatum</t>
   </si>
   <si>
-    <t>Condition.onsetPeriod.end</t>
+    <t>Condition.abatementDateTime</t>
   </si>
   <si>
     <t>Diagnose.KlinischRelevanterZeitraum.Lebensphase</t>
@@ -680,7 +674,7 @@
     <t>In welcher Lebensphase die Krankheit began</t>
   </si>
   <si>
-    <t>Condition.onsetPeriod.start.extension('http://fhir.de/StructureDefinition/lebensphase').valueCodeableConcept</t>
+    <t>Condition.onsetAge.extension('http://fhir.de/StructureDefinition/lebensphase').valueCodeableConcept</t>
   </si>
   <si>
     <t>Diagnose.KlinischRelevanterZeitraum.Lebensphase.bis</t>
@@ -689,7 +683,7 @@
     <t>In welcher Lebensphase die Krankheit endete</t>
   </si>
   <si>
-    <t>Condition.onsetPeriod.end.extension('http://fhir.de/StructureDefinition/lebensphase').valueCodeableConcept</t>
+    <t>Condition.abatementAge.extension('http://fhir.de/StructureDefinition/lebensphase').valueCodeableConcept</t>
   </si>
   <si>
     <t>Diagnose.Feststellungsdatum</t>
@@ -5017,15 +5011,15 @@
         <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>191</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5125,10 +5119,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5230,10 +5224,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5337,10 +5331,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5366,10 +5360,10 @@
         <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5420,7 +5414,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5435,15 +5429,15 @@
         <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>198</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5543,10 +5537,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5648,10 +5642,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5755,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5781,13 +5775,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5838,7 +5832,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -5853,15 +5847,15 @@
         <v>75</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5884,13 +5878,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5941,30 +5935,30 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5990,10 +5984,10 @@
         <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6044,7 +6038,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6064,10 +6058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6167,10 +6161,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6272,10 +6266,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6379,10 +6373,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6408,10 +6402,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6462,30 +6456,30 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK52" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6511,10 +6505,10 @@
         <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6565,30 +6559,30 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK53" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6611,13 +6605,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6668,7 +6662,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6683,15 +6677,15 @@
         <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6714,13 +6708,13 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6771,7 +6765,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -6786,7 +6780,7 @@
         <v>75</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-diagnose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
